--- a/Alcopalet_PyG_2025.xlsx
+++ b/Alcopalet_PyG_2025.xlsx
@@ -620,7 +620,7 @@
       </c>
       <c r="C6" s="8">
         <f>B6/$B$6</f>
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="C7" s="12">
         <f>B7/$B$6</f>
-        <v/>
+        <v>0.08201528940408487</v>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
       </c>
       <c r="C8" s="12">
         <f>B8/$B$6</f>
-        <v/>
+        <v>-0.6692098846152252</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -671,15 +671,15 @@
       </c>
       <c r="B9" s="14">
         <f>SUM(B6:B8)</f>
-        <v/>
+        <v>1892823.0</v>
       </c>
       <c r="C9" s="8">
         <f>B9/$B$6</f>
-        <v/>
+        <v>0.41280540478885963</v>
       </c>
       <c r="D9" s="15">
         <f>B9-1892822</f>
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="E9" s="9" t="n"/>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="C10" s="12">
         <f>B10/$B$6</f>
-        <v/>
+        <v>-0.10504513695712812</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -708,7 +708,7 @@
       </c>
       <c r="C11" s="12">
         <f>B11/$B$6</f>
-        <v/>
+        <v>-0.05849561214210645</v>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="C12" s="12">
         <f>B12/$B$6</f>
-        <v/>
+        <v>-0.06788961253510428</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
@@ -741,7 +741,7 @@
       </c>
       <c r="C13" s="12">
         <f>B13/$B$6</f>
-        <v/>
+        <v>-0.08265145737423797</v>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
@@ -757,15 +757,15 @@
       </c>
       <c r="B14" s="14">
         <f>B9+SUM(B10:B13)</f>
-        <v/>
+        <v>452674.0</v>
       </c>
       <c r="C14" s="8">
         <f>B14/$B$6</f>
-        <v/>
+        <v>0.0987235857802828</v>
       </c>
       <c r="D14" s="15">
         <f>B14-452674</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="9" t="n"/>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="C15" s="12">
         <f>B15/$B$6</f>
-        <v/>
+        <v>-0.007882419933233987</v>
       </c>
     </row>
     <row r="16">
@@ -791,11 +791,11 @@
       </c>
       <c r="B16" s="14">
         <f>B14+B15</f>
-        <v/>
+        <v>416531.0</v>
       </c>
       <c r="C16" s="8">
         <f>B16/$B$6</f>
-        <v/>
+        <v>0.09084116584704882</v>
       </c>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="C17" s="12">
         <f>B17/$B$6</f>
-        <v/>
+        <v>-0.009605983686446176</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
@@ -827,11 +827,11 @@
       </c>
       <c r="B18" s="14">
         <f>B16+B17</f>
-        <v/>
+        <v>372485.0</v>
       </c>
       <c r="C18" s="8">
         <f>B18/$B$6</f>
-        <v/>
+        <v>0.08123518216060265</v>
       </c>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="9" t="n"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C19" s="12">
         <f>B19/$B$6</f>
-        <v/>
+        <v>-0.020308741017698643</v>
       </c>
     </row>
     <row r="20">
@@ -858,15 +858,15 @@
       </c>
       <c r="B20" s="14">
         <f>B18+B19</f>
-        <v/>
+        <v>279364.0</v>
       </c>
       <c r="C20" s="8">
         <f>B20/$B$6</f>
-        <v/>
+        <v>0.060926441142904</v>
       </c>
       <c r="D20" s="15">
         <f>B20-279364</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E20" s="9" t="n"/>
     </row>
@@ -887,7 +887,6 @@
           <t>¿PARA QUÉ? Conectar el Anexo 1 con el escandallo del Anexo 3.</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr"/>
       <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Los 3.068.506 € son lo que se COMPRÓ. Si usas esa cifra, el Anexo 3 parece descuadrado y acabas descartándolo. Restando el aumento de existencias, ambos anexos cuadran y puedes apoyarte en el escandallo con confianza.</t>
@@ -902,7 +901,7 @@
       </c>
       <c r="B24" s="16">
         <f>-B8</f>
-        <v/>
+        <v>3068506.0</v>
       </c>
     </row>
     <row r="25">
@@ -913,7 +912,7 @@
       </c>
       <c r="B25" s="16">
         <f>-B7</f>
-        <v/>
+        <v>-376062.0</v>
       </c>
     </row>
     <row r="26">
@@ -924,11 +923,11 @@
       </c>
       <c r="B26" s="14">
         <f>-B8-B7</f>
-        <v/>
+        <v>2692444.0</v>
       </c>
       <c r="C26" s="8">
         <f>B26/B6</f>
-        <v/>
+        <v>0.5871945952111404</v>
       </c>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
@@ -956,7 +955,7 @@
       </c>
       <c r="B28" s="18">
         <f>B26-B27</f>
-        <v/>
+        <v>-288.0</v>
       </c>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="19" t="n"/>
@@ -983,7 +982,6 @@
           <t>¿PARA QUÉ? Es EL cálculo del caso.</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr"/>
       <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Persán es un pedido incremental, y un pedido incremental no se juzga con costes completos sino con margen de contribución. Sin esta separación no se puede decir nada del contrato.</t>
@@ -998,11 +996,11 @@
       </c>
       <c r="B32" s="16">
         <f>B26</f>
-        <v/>
+        <v>2692444.0</v>
       </c>
       <c r="C32" s="12">
         <f>B32/B6</f>
-        <v/>
+        <v>0.5871945952111404</v>
       </c>
     </row>
     <row r="33">
@@ -1013,11 +1011,11 @@
       </c>
       <c r="B33" s="16">
         <f>-B11</f>
-        <v/>
+        <v>268218.0</v>
       </c>
       <c r="C33" s="12">
         <f>B33/B6</f>
-        <v/>
+        <v>0.05849561214210645</v>
       </c>
     </row>
     <row r="34">
@@ -1028,11 +1026,11 @@
       </c>
       <c r="B34" s="16">
         <f>-B13</f>
-        <v/>
+        <v>378979.0</v>
       </c>
       <c r="C34" s="12">
         <f>B34/B6</f>
-        <v/>
+        <v>0.08265145737423797</v>
       </c>
     </row>
     <row r="35">
@@ -1043,11 +1041,11 @@
       </c>
       <c r="B35" s="14">
         <f>SUM(B32:B34)</f>
-        <v/>
+        <v>3339641.0</v>
       </c>
       <c r="C35" s="8">
         <f>B35/B6</f>
-        <v/>
+        <v>0.7283416647274847</v>
       </c>
       <c r="D35" s="9" t="n"/>
       <c r="E35" s="9" t="n"/>
@@ -1060,11 +1058,11 @@
       </c>
       <c r="B36" s="14">
         <f>B6-B35</f>
-        <v/>
+        <v>1245626.0</v>
       </c>
       <c r="C36" s="8">
         <f>B36/B6</f>
-        <v/>
+        <v>0.2716583352725152</v>
       </c>
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="21" t="inlineStr">
@@ -1081,11 +1079,11 @@
       </c>
       <c r="B37" s="16">
         <f>-B10</f>
-        <v/>
+        <v>481660.0</v>
       </c>
       <c r="C37" s="12">
         <f>B37/B6</f>
-        <v/>
+        <v>0.10504513695712812</v>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
@@ -1101,11 +1099,11 @@
       </c>
       <c r="B38" s="16">
         <f>-B12</f>
-        <v/>
+        <v>311292.0</v>
       </c>
       <c r="C38" s="12">
         <f>B38/B6</f>
-        <v/>
+        <v>0.06788961253510428</v>
       </c>
     </row>
     <row r="39">
@@ -1116,11 +1114,11 @@
       </c>
       <c r="B39" s="14">
         <f>B37+B38</f>
-        <v/>
+        <v>792952.0</v>
       </c>
       <c r="C39" s="8">
         <f>B39/B6</f>
-        <v/>
+        <v>0.1729347494922324</v>
       </c>
       <c r="D39" s="9" t="n"/>
       <c r="E39" s="9" t="n"/>
@@ -1133,11 +1131,11 @@
       </c>
       <c r="B40" s="22">
         <f>B36-B39</f>
-        <v/>
+        <v>452674.0</v>
       </c>
       <c r="C40" s="12">
         <f>B40/B6</f>
-        <v/>
+        <v>0.0987235857802828</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -1148,7 +1146,7 @@
       </c>
       <c r="B41" s="18">
         <f>B40-B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C41" s="19" t="n"/>
       <c r="D41" s="19" t="n"/>
@@ -1175,7 +1173,6 @@
           <t>¿PARA QUÉ? Medir el colchón y por qué Persán lo estrecha.</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr"/>
       <c r="E44" s="13" t="inlineStr">
         <is>
           <t>Persán empeora las dos variables a la vez: sube los costes fijos en 108.000 € (campa + leasing) Y aporta margen de contribución negativo. Eleva el punto muerto mientras reduce la capacidad de alcanzarlo.</t>
@@ -1190,7 +1187,7 @@
       </c>
       <c r="B45" s="23">
         <f>B36/B6</f>
-        <v/>
+        <v>0.2716583352725152</v>
       </c>
     </row>
     <row r="46">
@@ -1201,7 +1198,7 @@
       </c>
       <c r="B46" s="22">
         <f>B39/B45</f>
-        <v/>
+        <v>2918931.2347237454</v>
       </c>
     </row>
     <row r="47">
@@ -1212,7 +1209,7 @@
       </c>
       <c r="B47" s="14">
         <f>(B39-B15-B17)/B45</f>
-        <v/>
+        <v>3214114.5204475503</v>
       </c>
       <c r="C47" s="9" t="n"/>
       <c r="D47" s="9" t="n"/>
@@ -1226,7 +1223,7 @@
       </c>
       <c r="B48" s="16">
         <f>B6</f>
-        <v/>
+        <v>4585267.0</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
@@ -1237,7 +1234,7 @@
       </c>
       <c r="B49" s="24">
         <f>(B6-B47)/B6</f>
-        <v/>
+        <v>0.2990343811063673</v>
       </c>
       <c r="C49" s="19" t="n"/>
       <c r="D49" s="19" t="n"/>
@@ -1255,7 +1252,7 @@
       </c>
       <c r="B50" s="25">
         <f>B36/B14</f>
-        <v/>
+        <v>2.751706526109297</v>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
@@ -1280,7 +1277,6 @@
           <t>¿PARA QUÉ? Responder a los padres y al proyecto a la vez.</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr"/>
       <c r="E53" s="13" t="inlineStr">
         <is>
           <t>Hay dos peticiones de dinero sobre la mesa: la casa de los fundadores y los 643.000 € que exige Persán el primer año. La respuesta no está en el resultado neto, está aquí.</t>
@@ -1295,7 +1291,7 @@
       </c>
       <c r="B54" s="16">
         <f>B14</f>
-        <v/>
+        <v>452674.0</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
@@ -1306,7 +1302,7 @@
       </c>
       <c r="B55" s="16">
         <f>-B7</f>
-        <v/>
+        <v>-376062.0</v>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
@@ -1322,7 +1318,7 @@
       </c>
       <c r="B56" s="16">
         <f>B17</f>
-        <v/>
+        <v>-44046.0</v>
       </c>
     </row>
     <row r="57">
@@ -1333,7 +1329,7 @@
       </c>
       <c r="B57" s="16">
         <f>B19</f>
-        <v/>
+        <v>-93121.0</v>
       </c>
     </row>
     <row r="58">
@@ -1344,7 +1340,7 @@
       </c>
       <c r="B58" s="27">
         <f>SUM(B54:B57)</f>
-        <v/>
+        <v>-60555.0</v>
       </c>
       <c r="C58" s="28" t="n"/>
       <c r="D58" s="28" t="n"/>
@@ -1358,7 +1354,7 @@
       </c>
       <c r="B59" s="16">
         <f>B20</f>
-        <v/>
+        <v>279364.0</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1">
@@ -1369,7 +1365,7 @@
       </c>
       <c r="B60" s="27">
         <f>B20-B58</f>
-        <v/>
+        <v>339919.0</v>
       </c>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="28" t="n"/>
@@ -1385,7 +1381,6 @@
           <t>Aviso: no hay balance en el caso.</t>
         </is>
       </c>
-      <c r="B61" s="16" t="inlineStr"/>
       <c r="E61" s="13" t="inlineStr">
         <is>
           <t>Se ignoran clientes y proveedores, así que es una aproximación y hay que declararlo así en el informe. El acopio de madera puede ser puntual. La dirección del argumento se mantiene.</t>
@@ -1409,7 +1404,6 @@
           <t>¿PARA QUÉ? El caso no da balance, pero se puede reconstruir.</t>
         </is>
       </c>
-      <c r="B64" s="16" t="inlineStr"/>
       <c r="E64" s="13" t="inlineStr">
         <is>
           <t>Los gastos financieros divididos por el tipo del banco dan la deuda aproximada. Sirve para saber si la empresa puede asumir más.</t>
@@ -1434,7 +1428,7 @@
       </c>
       <c r="B66" s="22">
         <f>-B17/B65</f>
-        <v/>
+        <v>587280.0</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
@@ -1445,7 +1439,7 @@
       </c>
       <c r="B67" s="31">
         <f>B66/B14</f>
-        <v/>
+        <v>1.2973574802175516</v>
       </c>
       <c r="C67" s="19" t="n"/>
       <c r="D67" s="19" t="n"/>
@@ -1463,7 +1457,7 @@
       </c>
       <c r="B68" s="25">
         <f>B14/-B17</f>
-        <v/>
+        <v>10.277301003496344</v>
       </c>
     </row>
     <row r="69" ht="24" customHeight="1">
@@ -1474,7 +1468,7 @@
       </c>
       <c r="B69" s="16">
         <f>B66+190000+454356</f>
-        <v/>
+        <v>1231636.0</v>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
@@ -1490,7 +1484,7 @@
       </c>
       <c r="B70" s="16">
         <f>B14-154800</f>
-        <v/>
+        <v>297874.0</v>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
@@ -1506,7 +1500,7 @@
       </c>
       <c r="B71" s="32">
         <f>B69/B70</f>
-        <v/>
+        <v>4.13475496350806</v>
       </c>
       <c r="C71" s="28" t="n"/>
       <c r="D71" s="28" t="n"/>
@@ -1533,7 +1527,6 @@
           <t>¿PARA QUÉ? Comprobar si el Anexo 3 es optimista.</t>
         </is>
       </c>
-      <c r="B74" s="16" t="inlineStr"/>
       <c r="E74" s="13" t="inlineStr">
         <is>
           <t>El contrato exige DOS camiones de retén permanente en nave. Conviene comprobar si el coste de transporte que el escandallo asigna a Persán es coherente con lo que cuestan los camiones actuales.</t>
@@ -1548,7 +1541,7 @@
       </c>
       <c r="B75" s="16">
         <f>-B11</f>
-        <v/>
+        <v>268218.0</v>
       </c>
     </row>
     <row r="76">
@@ -1569,7 +1562,7 @@
       </c>
       <c r="B77" s="14">
         <f>B75/B76</f>
-        <v/>
+        <v>134109.0</v>
       </c>
       <c r="C77" s="9" t="n"/>
       <c r="D77" s="9" t="n"/>
@@ -1583,7 +1576,7 @@
       </c>
       <c r="B78" s="16">
         <f>0.53*90000</f>
-        <v/>
+        <v>47700.0</v>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
@@ -1599,7 +1592,7 @@
       </c>
       <c r="B79" s="27">
         <f>B77-B78</f>
-        <v/>
+        <v>86409.0</v>
       </c>
       <c r="C79" s="28" t="n"/>
       <c r="D79" s="28" t="n"/>
